--- a/website-sync/public/downloads/GanttSampleData.xlsx
+++ b/website-sync/public/downloads/GanttSampleData.xlsx
@@ -7,20 +7,24 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Tasks" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="How to use" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Start here" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tasks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$1:$F$13</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="166" formatCode="0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,18 +33,75 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000F3D36"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000F3D36"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001A6B5C"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="003D5A54"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001A6B5C"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F3D36"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F2EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A6B5C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3FAF7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,15 +109,51 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9D2"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9D2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9D2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9D2"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,293 +516,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000F3D36"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="82" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>End</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Duration</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Progress</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Resource</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Requirements</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>46027</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>46036</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Discovery</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Alex</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Wireframes</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>46034</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>46043</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Discovery</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>API Design</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>46037</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>46051</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Sam</t>
+          <t>DataLund Gantt chart</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Core task columns only — swap in your own rows</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Quick start</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Frontend</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>46044</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>46065</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Jordan</t>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>1. Import ganttChart.pbiviz</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>46044</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>46062</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Sam</t>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2. Load Tasks</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Alpha Gate</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>46065</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>46065</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Alex</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>46062</v>
-      </c>
-      <c r="D8" t="n">
-        <v>14</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Launch</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Riley</t>
-        </is>
-      </c>
-    </row>
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>3. Bind Task, Start Date, End Date — then Progress, Group, Resource</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>UAT</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>46072</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>46079</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Launch</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Alex</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Go-Live</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>46082</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>46082</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Launch</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Alex</t>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Same columns as Resource Load. Full suite page → DatalundSuiteSample.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>https://datalund.no/visuals/gantt/</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -713,51 +608,367 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001A6B5C"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Power BI Desktop test data for the custom Gantt visual</t>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Start Date</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>End Date</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Progress</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>Resource</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Requirements</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C2" s="11" t="n">
+        <v>46198</v>
+      </c>
+      <c r="D2" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>Ada Ng</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1. Home → Get data → Excel workbook → select this file → load Tasks.</t>
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>API design</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C3" s="14" t="n">
+        <v>46223</v>
+      </c>
+      <c r="D3" s="15" t="n">
+        <v>75</v>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>Sam Ortiz</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2. Import GanttChart.pbiviz (Visualizations … → Import a visual from a file).</t>
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>FAT prep</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C4" s="11" t="n">
+        <v>46270</v>
+      </c>
+      <c r="D4" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Ada Ng</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>3. Bind: Task→Task, Start Date→Start, End Date→End, Duration→Duration (optional extras: Progress, Group, Resource).</t>
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Cable pull</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>46254</v>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>Bo Berg</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Alpha Gate and Go-Live are zero-duration milestones. QA uses Duration instead of End.</t>
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Weather hold</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>46252</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Riley Chen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>On-call week</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>46252</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>46258</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>Bo Berg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Scope workshop</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>46214</v>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>46228</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Initiation</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>Cara Diaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Scope freeze</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>46246</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>46246</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Initiation</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Cara Diaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>46244</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>Sam Ortiz</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>UAT</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>46259</v>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>Ada Ng</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Permit draft</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>46249</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>46296</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>Finn Olsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Stakeholder map</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>46280</v>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>Jordan Lee</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>